--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.290493990494232</v>
+        <v>1.347205273455313</v>
       </c>
       <c r="D2" t="n">
-        <v>5.084479218228466</v>
+        <v>0.8262278729621259</v>
       </c>
       <c r="E2" t="n">
-        <v>8.957796595222746</v>
+        <v>1.455641946723696</v>
       </c>
       <c r="F2" t="n">
-        <v>12.96576750281095</v>
+        <v>2.106937219206779</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.20608718093972</v>
+        <v>4.258489166902705</v>
       </c>
       <c r="D3" t="n">
-        <v>31.01601422385036</v>
+        <v>5.040102311375684</v>
       </c>
       <c r="E3" t="n">
-        <v>8.957796595222746</v>
+        <v>1.455641946723696</v>
       </c>
       <c r="F3" t="n">
-        <v>12.96576750281095</v>
+        <v>2.106937219206779</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
